--- a/output/result_final.xlsx
+++ b/output/result_final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -464,7 +464,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -474,27 +474,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Rochester, NY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 26B </t>
+          <t xml:space="preserve"> 6B </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diversified Real Estate</t>
+          <t>Net Lease REIT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -514,12 +514,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (redirect)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://broadstone.com/</t>
         </is>
       </c>
     </row>

--- a/output/result_final.xlsx
+++ b/output/result_final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20430" windowHeight="8160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -461,10 +461,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Barings Real Estate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -474,27 +474,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rochester, NY</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6B </t>
+          <t>27B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.barings.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Net Lease REIT</t>
+          <t>Diversified Real Estate</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://www.linkedin.com/company/barings</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -519,11 +519,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://broadstone.com/</t>
+          <t>https://www.barings.com/guest</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/result_final.xlsx
+++ b/output/result_final.xlsx
@@ -1,33 +1,175 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Headquarters</t>
+  </si>
+  <si>
+    <t>Total AUM (USD)</t>
+  </si>
+  <si>
+    <t>Official Website</t>
+  </si>
+  <si>
+    <t>REIT Focus / Asset Type</t>
+  </si>
+  <si>
+    <t>Realty Income Corporation</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>20B</t>
+  </si>
+  <si>
+    <t>https://www.realtyincome.com</t>
+  </si>
+  <si>
+    <t>Net Lease REIT</t>
+  </si>
+  <si>
+    <t>STORE Capital</t>
+  </si>
+  <si>
+    <t>Scottsdale, AZ</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>https://www.storecapital.com</t>
+  </si>
+  <si>
+    <t>Physicians Realty Trust</t>
+  </si>
+  <si>
+    <t>Milwaukee, WI</t>
+  </si>
+  <si>
+    <t>5B</t>
+  </si>
+  <si>
+    <t>https://www.docreit.com</t>
+  </si>
+  <si>
+    <t>Healthcare REIT</t>
+  </si>
+  <si>
+    <t>Eastdil Secured</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>10B</t>
+  </si>
+  <si>
+    <t>https://www.eastdilsecured.com</t>
+  </si>
+  <si>
+    <t>Real Estate Capital</t>
+  </si>
+  <si>
+    <t>Mack-Cali Realty</t>
+  </si>
+  <si>
+    <t>Jersey City, NJ</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>https://www.mack-cali.com</t>
+  </si>
+  <si>
+    <t>Office/Multifamily REIT</t>
+  </si>
+  <si>
+    <t>COMPANY_LINKEDIN_URL_HEADER</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/realty-income-corporation</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/store-capital</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/healthpeak/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/eastdil-secured/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/mack-cali-realty-corporation/</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF374151"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -45,81 +187,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -385,149 +472,163 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="19.42578125" customWidth="1" min="1" max="1"/>
-    <col width="27.28515625" customWidth="1" min="3" max="3"/>
-    <col width="26.140625" customWidth="1" min="4" max="4"/>
-    <col width="34.28515625" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="34.28515625" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Company Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Headquarters</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Total AUM (USD)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Official Website</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>REIT Focus / Asset Type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Profile URL</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Scrape Method</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>URL Valid (syntax)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>URL Status (live)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Website Status</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Website Final URL</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CenterSquare Investment Management</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12B</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://centersquare.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Listed REIT Securities</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>step3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://centersquare.com</t>
-        </is>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>